--- a/data/trans_dic/IP08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 15,55</t>
+          <t>4,5; 15,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 20,02</t>
+          <t>8,75; 20,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 15,65</t>
+          <t>3,16; 13,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 44,94</t>
+          <t>5,33; 46,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 18,27</t>
+          <t>7,84; 19,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 20,31</t>
+          <t>8,32; 21,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,18</t>
+          <t>1,04; 9,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 27,75</t>
+          <t>10,76; 28,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 14,37</t>
+          <t>6,99; 14,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 18,29</t>
+          <t>9,88; 18,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 10,04</t>
+          <t>2,87; 9,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,38; 30,74</t>
+          <t>10,75; 32,81</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 9,5</t>
+          <t>5,52; 9,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 14,74</t>
+          <t>9,84; 14,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,75</t>
+          <t>4,76; 8,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,52</t>
+          <t>5,87; 10,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,97; 13,67</t>
+          <t>9,01; 13,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,75</t>
+          <t>11,75; 16,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 10,17</t>
+          <t>6,04; 10,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 19,34</t>
+          <t>9,63; 19,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,9; 10,99</t>
+          <t>7,95; 11,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,55; 15,08</t>
+          <t>11,35; 15,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,82</t>
+          <t>6,08; 8,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 13,92</t>
+          <t>8,74; 14,62</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 14,51</t>
+          <t>7,05; 14,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 13,78</t>
+          <t>5,95; 13,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 10,49</t>
+          <t>4,2; 10,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,98</t>
+          <t>7,45; 16,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,6; 17,09</t>
+          <t>8,96; 17,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 16,29</t>
+          <t>7,97; 16,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,62</t>
+          <t>3,2; 8,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,19; 17,66</t>
+          <t>8,01; 17,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 14,46</t>
+          <t>8,47; 14,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 13,49</t>
+          <t>8,14; 13,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,37</t>
+          <t>4,33; 8,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 15,21</t>
+          <t>8,86; 15,05</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,17</t>
+          <t>6,51; 10,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,9; 13,54</t>
+          <t>9,95; 13,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,49</t>
+          <t>5,29; 8,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,41</t>
+          <t>7,35; 12,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 13,62</t>
+          <t>9,83; 13,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,74; 15,8</t>
+          <t>11,63; 15,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,51</t>
+          <t>5,56; 8,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 17,19</t>
+          <t>10,61; 17,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,7; 11,28</t>
+          <t>8,75; 11,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 14,1</t>
+          <t>11,25; 14,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,07</t>
+          <t>5,73; 7,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,07</t>
+          <t>9,69; 14,55</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,85%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7818</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12746</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9382</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>10908</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>18185</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24297</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7222</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>20290</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4090; 13925</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8082; 18712</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1874; 8302</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2913; 25527</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6808; 16838</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7174; 18414</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>712; 6445</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6674; 17506</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12430; 26213</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17649; 32216</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3679; 12127</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>12544; 38287</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>30560</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54883</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31600</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37573</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>53441</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70395</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>65817</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>84000</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>125278</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>70116</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>103390</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>22968; 39662</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>44510; 66749</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22434; 41373</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>26974; 48276</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>42902; 64068</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>58073; 83580</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>29370; 48729</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>49548; 100667</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>70922; 98691</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>107453; 143039</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>58185; 85807</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>85152; 142362</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>17866</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15240</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11597</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16593</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20474</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>22304</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>37536</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>35714</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>21756</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>38897</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>12270; 25372</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9878; 22134</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7212; 17799</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11138; 24289</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>14166; 26892</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13725; 28038</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5974; 16652</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>14695; 31866</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>28150; 47528</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>27543; 46783</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15526; 30210</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>29490; 50117</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>56243</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82869</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>47647</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>63548</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>99029</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>139721</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>185289</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>99093</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>162578</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>44360; 69145</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>70716; 97881</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37149; 58633</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>48787; 83524</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>70873; 98430</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>87568; 119466</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>41248; 63708</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>80646; 131983</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>122752; 158112</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>164687; 206097</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>82772; 114153</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>137982; 207159</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 15,32</t>
+          <t>4,4; 14,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,75; 20,26</t>
+          <t>8,91; 20,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 13,98</t>
+          <t>3,09; 14,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 46,69</t>
+          <t>4,81; 45,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,84; 19,39</t>
+          <t>7,03; 18,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,32; 21,36</t>
+          <t>8,25; 20,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,39</t>
+          <t>1,0; 9,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,76; 28,23</t>
+          <t>9,91; 26,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 14,75</t>
+          <t>6,86; 15,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,88; 18,04</t>
+          <t>9,76; 18,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 9,47</t>
+          <t>2,96; 9,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 32,81</t>
+          <t>10,62; 29,61</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,53</t>
+          <t>5,53; 9,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 14,76</t>
+          <t>9,88; 14,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,78</t>
+          <t>5,07; 8,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,51</t>
+          <t>6,1; 10,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 13,45</t>
+          <t>9,13; 13,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,75; 16,9</t>
+          <t>11,76; 16,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,02</t>
+          <t>6,05; 10,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 19,56</t>
+          <t>9,7; 19,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,06</t>
+          <t>7,95; 11,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 15,11</t>
+          <t>11,64; 15,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 8,96</t>
+          <t>6,02; 8,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 14,62</t>
+          <t>8,77; 14,59</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 14,58</t>
+          <t>7,13; 14,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,33</t>
+          <t>5,95; 13,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,36</t>
+          <t>4,06; 10,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 16,24</t>
+          <t>7,5; 15,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,96; 17,01</t>
+          <t>8,89; 17,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,28</t>
+          <t>7,8; 16,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 8,91</t>
+          <t>3,16; 8,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 17,38</t>
+          <t>8,22; 17,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 14,31</t>
+          <t>8,58; 14,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,14; 13,83</t>
+          <t>8,07; 13,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,42</t>
+          <t>4,07; 8,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 15,05</t>
+          <t>8,84; 15,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,15</t>
+          <t>6,68; 10,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,95; 13,77</t>
+          <t>9,79; 13,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,35</t>
+          <t>5,3; 8,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 12,59</t>
+          <t>7,41; 12,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 13,65</t>
+          <t>9,56; 13,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,63; 15,87</t>
+          <t>11,64; 15,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,59</t>
+          <t>5,45; 8,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,61; 17,37</t>
+          <t>10,59; 17,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 11,28</t>
+          <t>8,58; 11,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 14,08</t>
+          <t>11,33; 14,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 7,91</t>
+          <t>5,76; 8,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 14,55</t>
+          <t>9,72; 14,23</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4090; 13925</t>
+          <t>3996; 13204</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8082; 18712</t>
+          <t>8232; 19062</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1874; 8302</t>
+          <t>1836; 8526</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2913; 25527</t>
+          <t>2628; 24815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6808; 16838</t>
+          <t>6105; 16232</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7174; 18414</t>
+          <t>7111; 17583</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>712; 6445</t>
+          <t>686; 6799</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6674; 17506</t>
+          <t>6143; 16606</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12430; 26213</t>
+          <t>12192; 26648</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17649; 32216</t>
+          <t>17433; 33074</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3679; 12127</t>
+          <t>3789; 12610</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12544; 38287</t>
+          <t>12397; 34551</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22968; 39662</t>
+          <t>22996; 39833</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44510; 66749</t>
+          <t>44663; 67524</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22434; 41373</t>
+          <t>23868; 41580</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26974; 48276</t>
+          <t>27995; 48721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42902; 64068</t>
+          <t>43465; 64741</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58073; 83580</t>
+          <t>58141; 83638</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29370; 48729</t>
+          <t>29445; 50360</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49548; 100667</t>
+          <t>49918; 97788</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70922; 98691</t>
+          <t>70963; 99720</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>107453; 143039</t>
+          <t>110172; 144729</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58185; 85807</t>
+          <t>57677; 84476</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85152; 142362</t>
+          <t>85373; 142070</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12270; 25372</t>
+          <t>12407; 25374</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9878; 22134</t>
+          <t>9888; 21819</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7212; 17799</t>
+          <t>6974; 17652</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11138; 24289</t>
+          <t>11221; 23834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14166; 26892</t>
+          <t>14054; 27324</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13725; 28038</t>
+          <t>13433; 28413</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5974; 16652</t>
+          <t>5904; 16546</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14695; 31866</t>
+          <t>15064; 32130</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28150; 47528</t>
+          <t>28519; 47400</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27543; 46783</t>
+          <t>27316; 45110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15526; 30210</t>
+          <t>14610; 29946</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29490; 50117</t>
+          <t>29425; 49940</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44360; 69145</t>
+          <t>45465; 68573</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70716; 97881</t>
+          <t>69593; 97242</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37149; 58633</t>
+          <t>37234; 59554</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48787; 83524</t>
+          <t>49163; 83139</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70873; 98430</t>
+          <t>68929; 97324</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87568; 119466</t>
+          <t>87653; 118574</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41248; 63708</t>
+          <t>40454; 62554</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80646; 131983</t>
+          <t>80504; 133640</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>122752; 158112</t>
+          <t>120248; 157045</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>164687; 206097</t>
+          <t>165828; 207723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82772; 114153</t>
+          <t>83244; 115865</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>137982; 207159</t>
+          <t>138405; 202596</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,94%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,6%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13,8%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,49%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,16%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,94%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 14,53</t>
+          <t>7,11; 18,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 20,64</t>
+          <t>8,14; 20,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 14,36</t>
+          <t>1,12; 10,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 45,38</t>
+          <t>10,18; 26,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 18,69</t>
+          <t>4,73; 15,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,25; 20,4</t>
+          <t>8,86; 20,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,91</t>
+          <t>3,29; 15,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,91; 26,78</t>
+          <t>4,05; 18,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 15,0</t>
+          <t>6,63; 14,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,76; 18,52</t>
+          <t>9,59; 18,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,85</t>
+          <t>2,88; 10,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 29,61</t>
+          <t>8,54; 20,52</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,55%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>12,14%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>6,71%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -857,52 +857,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,57</t>
+          <t>8,97; 13,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 14,93</t>
+          <t>11,66; 16,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,83</t>
+          <t>6,15; 10,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 10,61</t>
+          <t>9,55; 18,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,59</t>
+          <t>5,43; 9,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,76; 16,92</t>
+          <t>9,72; 14,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,35</t>
+          <t>4,94; 8,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 19,0</t>
+          <t>6,67; 11,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,17</t>
+          <t>7,9; 10,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,29</t>
+          <t>11,55; 15,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,77; 14,59</t>
+          <t>8,87; 13,58</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,89%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10,26%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,18%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,75%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,44%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 14,58</t>
+          <t>8,6; 17,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,14</t>
+          <t>7,94; 16,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 10,27</t>
+          <t>3,16; 8,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 15,94</t>
+          <t>7,85; 17,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 17,28</t>
+          <t>6,82; 14,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,8; 16,5</t>
+          <t>6,35; 13,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,86</t>
+          <t>4,3; 10,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,22; 17,52</t>
+          <t>7,62; 16,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 14,27</t>
+          <t>8,77; 14,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 13,33</t>
+          <t>7,93; 13,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,35</t>
+          <t>4,4; 8,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,84; 15,0</t>
+          <t>8,66; 15,06</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11,66%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,79%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,07</t>
+          <t>9,56; 13,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,68</t>
+          <t>11,74; 15,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,48</t>
+          <t>5,57; 8,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 12,53</t>
+          <t>10,22; 16,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 13,49</t>
+          <t>6,7; 10,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,75</t>
+          <t>9,9; 13,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,43</t>
+          <t>5,26; 8,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 17,58</t>
+          <t>7,52; 11,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 11,2</t>
+          <t>8,7; 11,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 14,19</t>
+          <t>11,29; 14,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,02</t>
+          <t>5,86; 8,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,72; 14,23</t>
+          <t>9,46; 13,38</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7818</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>12746</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4449</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>14048</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3996; 13204</t>
+          <t>6175; 15866</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8232; 19062</t>
+          <t>7018; 17503</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1836; 8526</t>
+          <t>771; 6987</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2628; 24815</t>
+          <t>5776; 15240</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6105; 16232</t>
+          <t>4294; 14130</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7111; 17583</t>
+          <t>8182; 18492</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>686; 6799</t>
+          <t>1952; 9295</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6143; 16606</t>
+          <t>1892; 8745</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12192; 26648</t>
+          <t>11781; 25544</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17433; 33074</t>
+          <t>17130; 32667</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3789; 12610</t>
+          <t>3685; 12849</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12397; 34551</t>
+          <t>8839; 21238</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>53441</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70395</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>59427</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>30560</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>54883</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>31600</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37573</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>53441</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70395</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>65817</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>103390</t>
+          <t>96913</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22996; 39833</t>
+          <t>42705; 65111</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44663; 67524</t>
+          <t>57676; 82804</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23868; 41580</t>
+          <t>29921; 49463</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27995; 48721</t>
+          <t>45234; 87264</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43465; 64741</t>
+          <t>22581; 39532</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58141; 83638</t>
+          <t>43962; 66639</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29445; 50360</t>
+          <t>23274; 41219</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49918; 97788</t>
+          <t>28748; 47686</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70963; 99720</t>
+          <t>70542; 98102</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>110172; 144729</t>
+          <t>109299; 142757</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57677; 84476</t>
+          <t>57646; 84411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85373; 142070</t>
+          <t>80204; 122902</t>
         </is>
       </c>
     </row>
@@ -1784,37 +1784,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20474</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19779</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>17866</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>15240</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>11597</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16593</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>19670</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20474</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>36993</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12407; 25374</t>
+          <t>13601; 27024</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9888; 21819</t>
+          <t>13680; 28061</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6974; 17652</t>
+          <t>5898; 16109</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11221; 23834</t>
+          <t>13229; 28665</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14054; 27324</t>
+          <t>11866; 25261</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13433; 28413</t>
+          <t>10538; 22878</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5904; 16546</t>
+          <t>7391; 18016</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15064; 32130</t>
+          <t>11436; 25167</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28519; 47400</t>
+          <t>29127; 48049</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27316; 45110</t>
+          <t>26831; 45635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14610; 29946</t>
+          <t>15773; 30016</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29425; 49940</t>
+          <t>27583; 47964</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>47647</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45465; 68573</t>
+          <t>68973; 98232</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69593; 97242</t>
+          <t>88371; 118979</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37234; 59554</t>
+          <t>41347; 63119</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49163; 83139</t>
+          <t>71419; 114800</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68929; 97324</t>
+          <t>45625; 69264</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87653; 118574</t>
+          <t>70360; 96227</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40454; 62554</t>
+          <t>36956; 59632</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80504; 133640</t>
+          <t>47230; 72252</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120248; 157045</t>
+          <t>122057; 158165</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>165828; 207723</t>
+          <t>165192; 206381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83244; 115865</t>
+          <t>84660; 116464</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>138405; 202596</t>
+          <t>125466; 177545</t>
         </is>
       </c>
     </row>
